--- a/artfynd/A 28495-2023 artfynd.xlsx
+++ b/artfynd/A 28495-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28495-2023 artfynd.xlsx
+++ b/artfynd/A 28495-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106780370</v>
+        <v>77346030</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>(A2515), Bockrössle, Sm</t>
+          <t>Nr33, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565539.5642028968</v>
+        <v>565420</v>
       </c>
       <c r="R2" t="n">
-        <v>6414055.468420305</v>
+        <v>6414016</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,34 +762,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jan Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jan Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106780385</v>
+        <v>106780359</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,11 +808,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -852,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565513.8170578406</v>
+        <v>565536</v>
       </c>
       <c r="R3" t="n">
-        <v>6414065.157808556</v>
+        <v>6414071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +856,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106780359</v>
+        <v>106780370</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,7 +914,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -973,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565535.5729229394</v>
+        <v>565540</v>
       </c>
       <c r="R4" t="n">
-        <v>6414071.36591231</v>
+        <v>6414055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +966,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +993,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106780385</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>(A2515), Bockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565514</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6414065</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
